--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I562"/>
+  <dimension ref="A1:I565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18982,6 +18982,105 @@
       <c r="I562" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>360.47</v>
+      </c>
+      <c r="C563" t="n">
+        <v>353.44</v>
+      </c>
+      <c r="D563" t="n">
+        <v>348.93</v>
+      </c>
+      <c r="E563" t="n">
+        <v>345.17</v>
+      </c>
+      <c r="F563" t="n">
+        <v>333.12</v>
+      </c>
+      <c r="G563" t="n">
+        <v>327.48</v>
+      </c>
+      <c r="H563" t="n">
+        <v>316.08</v>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>358.23</v>
+      </c>
+      <c r="C564" t="n">
+        <v>351.35</v>
+      </c>
+      <c r="D564" t="n">
+        <v>348.13</v>
+      </c>
+      <c r="E564" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="F564" t="n">
+        <v>332.03</v>
+      </c>
+      <c r="G564" t="n">
+        <v>326.81</v>
+      </c>
+      <c r="H564" t="n">
+        <v>315.93</v>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:16+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="C565" t="n">
+        <v>350.56</v>
+      </c>
+      <c r="D565" t="n">
+        <v>347.81</v>
+      </c>
+      <c r="E565" t="n">
+        <v>342.76</v>
+      </c>
+      <c r="F565" t="n">
+        <v>332.41</v>
+      </c>
+      <c r="G565" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="H565" t="n">
+        <v>323.81</v>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18996,7 +19095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B671"/>
+  <dimension ref="A1:B675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25709,6 +25808,46 @@
       </c>
       <c r="B671" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-06-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-07-05 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -25877,28 +26016,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.187915000174664</v>
+        <v>-0.1823144330136596</v>
       </c>
       <c r="J2" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K2" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05096176135754704</v>
+        <v>0.0485023256591024</v>
       </c>
       <c r="M2" t="n">
-        <v>4.787251542054353</v>
+        <v>4.783089847191549</v>
       </c>
       <c r="N2" t="n">
-        <v>35.72331583227976</v>
+        <v>35.67942605337421</v>
       </c>
       <c r="O2" t="n">
-        <v>5.976898512797399</v>
+        <v>5.973225766147987</v>
       </c>
       <c r="P2" t="n">
-        <v>358.5327861311866</v>
+        <v>358.4733197421837</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25955,28 +26094,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1951003998129404</v>
+        <v>0.1946415415579618</v>
       </c>
       <c r="J3" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K3" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03749606528796412</v>
+        <v>0.03777454845029227</v>
       </c>
       <c r="M3" t="n">
-        <v>6.197683044426312</v>
+        <v>6.171832468666245</v>
       </c>
       <c r="N3" t="n">
-        <v>53.07899849059567</v>
+        <v>52.80550728321786</v>
       </c>
       <c r="O3" t="n">
-        <v>7.285533507616012</v>
+        <v>7.26673979740694</v>
       </c>
       <c r="P3" t="n">
-        <v>346.9770240954372</v>
+        <v>346.9819069139942</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26033,28 +26172,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1069672914163499</v>
+        <v>0.1075808042135191</v>
       </c>
       <c r="J4" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K4" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01961918713034549</v>
+        <v>0.02008445249381974</v>
       </c>
       <c r="M4" t="n">
-        <v>4.50092661974508</v>
+        <v>4.479634282964678</v>
       </c>
       <c r="N4" t="n">
-        <v>31.06028064985192</v>
+        <v>30.89788934440639</v>
       </c>
       <c r="O4" t="n">
-        <v>5.573175095926192</v>
+        <v>5.558586991709889</v>
       </c>
       <c r="P4" t="n">
-        <v>344.8706513254558</v>
+        <v>344.8641396481713</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26111,28 +26250,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3180159431385622</v>
+        <v>0.3192575513809148</v>
       </c>
       <c r="J5" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K5" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1572811068885352</v>
+        <v>0.1599418463736053</v>
       </c>
       <c r="M5" t="n">
-        <v>4.529655813897467</v>
+        <v>4.510160633027802</v>
       </c>
       <c r="N5" t="n">
-        <v>29.43699974313706</v>
+        <v>29.29275319522124</v>
       </c>
       <c r="O5" t="n">
-        <v>5.425587502117818</v>
+        <v>5.412278004243799</v>
       </c>
       <c r="P5" t="n">
-        <v>334.1199887244014</v>
+        <v>334.1068110539458</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26189,28 +26328,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4049946862796274</v>
+        <v>0.4044985509864556</v>
       </c>
       <c r="J6" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K6" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2272402827420594</v>
+        <v>0.2290086158111144</v>
       </c>
       <c r="M6" t="n">
-        <v>4.562061032696852</v>
+        <v>4.541370989131924</v>
       </c>
       <c r="N6" t="n">
-        <v>30.30033209140692</v>
+        <v>30.14131758328464</v>
       </c>
       <c r="O6" t="n">
-        <v>5.504573742934771</v>
+        <v>5.490110889889625</v>
       </c>
       <c r="P6" t="n">
-        <v>322.1322232385272</v>
+        <v>322.1374944562475</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26267,28 +26406,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3507527266344657</v>
+        <v>0.3532669667420211</v>
       </c>
       <c r="J7" t="n">
+        <v>564</v>
+      </c>
+      <c r="K7" t="n">
         <v>561</v>
       </c>
-      <c r="K7" t="n">
-        <v>558</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1959868882610221</v>
+        <v>0.1998539735867909</v>
       </c>
       <c r="M7" t="n">
-        <v>4.248934926688795</v>
+        <v>4.238217628613424</v>
       </c>
       <c r="N7" t="n">
-        <v>27.45004750285127</v>
+        <v>27.37065169944301</v>
       </c>
       <c r="O7" t="n">
-        <v>5.239279292312185</v>
+        <v>5.231696827936707</v>
       </c>
       <c r="P7" t="n">
-        <v>317.4031402145378</v>
+        <v>317.3763829184302</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26345,28 +26484,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05095492291161864</v>
+        <v>0.05720464963891496</v>
       </c>
       <c r="J8" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K8" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005187951673201519</v>
+        <v>0.006553584321853823</v>
       </c>
       <c r="M8" t="n">
-        <v>4.161761398676282</v>
+        <v>4.174598211192444</v>
       </c>
       <c r="N8" t="n">
-        <v>27.04624616953268</v>
+        <v>27.14305989507826</v>
       </c>
       <c r="O8" t="n">
-        <v>5.200600558544433</v>
+        <v>5.209900180913091</v>
       </c>
       <c r="P8" t="n">
-        <v>311.5585214746312</v>
+        <v>311.4921220170107</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26404,7 +26543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I562"/>
+  <dimension ref="A1:I565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52809,6 +52948,147 @@
         </is>
       </c>
     </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-36.95323560159412,175.8416793292634</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-36.95396158406093,175.84165129515543</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-36.95467659517796,175.84178939284868</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-36.95537739734058,175.84207439088124</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>-36.956070620943926,175.84241027423266</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>-36.95672655654885,175.84289013924294</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>-36.95732282502388,175.84347420347095</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-36.95323713175623,175.84165426159205</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-36.953964436775955,175.8416281092286</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-36.95467875776541,175.8417808279707</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-36.95538463024321,175.8420560596911</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>-36.95607595049201,175.84239999978885</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>-36.956730520122946,175.84288446854646</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>-36.95732381336384,175.8434730555466</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:16+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-36.95323789683531,175.84164172775587</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-36.953965515073776,175.84161934516962</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-36.95467962280023,175.84177740201935</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-36.95538697497482,175.84205011716165</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-36.95607409248451,175.8424035817052</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-36.95669431552662,175.84293626652817</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-36.95727189255739,175.84353335979915</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I565"/>
+  <dimension ref="A1:I569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19073,14 +19073,146 @@
         <v>332.41</v>
       </c>
       <c r="G565" t="n">
-        <v>332.93</v>
+        <v>326.34</v>
       </c>
       <c r="H565" t="n">
-        <v>323.81</v>
+        <v>315.32</v>
       </c>
       <c r="I565" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>357.94</v>
+      </c>
+      <c r="C566" t="n">
+        <v>352.75</v>
+      </c>
+      <c r="D566" t="n">
+        <v>349.42</v>
+      </c>
+      <c r="E566" t="n">
+        <v>344.01</v>
+      </c>
+      <c r="F566" t="n">
+        <v>333.01</v>
+      </c>
+      <c r="G566" t="n">
+        <v>327.41</v>
+      </c>
+      <c r="H566" t="n">
+        <v>315.61</v>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>359.11</v>
+      </c>
+      <c r="C567" t="n">
+        <v>354.04</v>
+      </c>
+      <c r="D567" t="n">
+        <v>350.34</v>
+      </c>
+      <c r="E567" t="n">
+        <v>344.78</v>
+      </c>
+      <c r="F567" t="n">
+        <v>333.35</v>
+      </c>
+      <c r="G567" t="n">
+        <v>328.17</v>
+      </c>
+      <c r="H567" t="n">
+        <v>315.36</v>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>363.33</v>
+      </c>
+      <c r="C568" t="n">
+        <v>354.85</v>
+      </c>
+      <c r="D568" t="n">
+        <v>350</v>
+      </c>
+      <c r="E568" t="n">
+        <v>343.66</v>
+      </c>
+      <c r="F568" t="n">
+        <v>332.29</v>
+      </c>
+      <c r="G568" t="n">
+        <v>328.17</v>
+      </c>
+      <c r="H568" t="n">
+        <v>315.36</v>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>363.39</v>
+      </c>
+      <c r="C569" t="n">
+        <v>354.09</v>
+      </c>
+      <c r="D569" t="n">
+        <v>350</v>
+      </c>
+      <c r="E569" t="n">
+        <v>343</v>
+      </c>
+      <c r="F569" t="n">
+        <v>332.36</v>
+      </c>
+      <c r="G569" t="n">
+        <v>327.72</v>
+      </c>
+      <c r="H569" t="n">
+        <v>315.47</v>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B675"/>
+  <dimension ref="A1:B681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25848,6 +25980,66 @@
       </c>
       <c r="B675" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-08-14 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -26016,28 +26208,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1823144330136596</v>
+        <v>-0.1716565187365519</v>
       </c>
       <c r="J2" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K2" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0485023256591024</v>
+        <v>0.04344127986526081</v>
       </c>
       <c r="M2" t="n">
-        <v>4.783089847191549</v>
+        <v>4.790825898506314</v>
       </c>
       <c r="N2" t="n">
-        <v>35.67942605337421</v>
+        <v>35.84410156328063</v>
       </c>
       <c r="O2" t="n">
-        <v>5.973225766147987</v>
+        <v>5.986994368068224</v>
       </c>
       <c r="P2" t="n">
-        <v>358.4733197421837</v>
+        <v>358.3595742180693</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26094,28 +26286,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1946415415579618</v>
+        <v>0.1971271580707542</v>
       </c>
       <c r="J3" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K3" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03777454845029227</v>
+        <v>0.03931436332697236</v>
       </c>
       <c r="M3" t="n">
-        <v>6.171832468666245</v>
+        <v>6.137640578777244</v>
       </c>
       <c r="N3" t="n">
-        <v>52.80550728321786</v>
+        <v>52.45791766357572</v>
       </c>
       <c r="O3" t="n">
-        <v>7.26673979740694</v>
+        <v>7.24278383382907</v>
       </c>
       <c r="P3" t="n">
-        <v>346.9819069139942</v>
+        <v>346.9553809311769</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26172,28 +26364,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1075808042135191</v>
+        <v>0.110737401312095</v>
       </c>
       <c r="J4" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K4" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02008445249381974</v>
+        <v>0.02158077775266976</v>
       </c>
       <c r="M4" t="n">
-        <v>4.479634282964678</v>
+        <v>4.461462359452821</v>
       </c>
       <c r="N4" t="n">
-        <v>30.89788934440639</v>
+        <v>30.71387512579782</v>
       </c>
       <c r="O4" t="n">
-        <v>5.558586991709889</v>
+        <v>5.54201002577565</v>
       </c>
       <c r="P4" t="n">
-        <v>344.8641396481713</v>
+        <v>344.8304623161018</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26250,28 +26442,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3192575513809148</v>
+        <v>0.3209526054453389</v>
       </c>
       <c r="J5" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K5" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1599418463736053</v>
+        <v>0.163575994598583</v>
       </c>
       <c r="M5" t="n">
-        <v>4.510160633027802</v>
+        <v>4.484560429853493</v>
       </c>
       <c r="N5" t="n">
-        <v>29.29275319522124</v>
+        <v>29.09891560002339</v>
       </c>
       <c r="O5" t="n">
-        <v>5.412278004243799</v>
+        <v>5.394341071903351</v>
       </c>
       <c r="P5" t="n">
-        <v>334.1068110539458</v>
+        <v>334.0887373979393</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26328,28 +26520,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4044985509864556</v>
+        <v>0.404126196948363</v>
       </c>
       <c r="J6" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K6" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2290086158111144</v>
+        <v>0.2316206193417861</v>
       </c>
       <c r="M6" t="n">
-        <v>4.541370989131924</v>
+        <v>4.512935085244192</v>
       </c>
       <c r="N6" t="n">
-        <v>30.14131758328464</v>
+        <v>29.93095446145872</v>
       </c>
       <c r="O6" t="n">
-        <v>5.490110889889625</v>
+        <v>5.470918977782318</v>
       </c>
       <c r="P6" t="n">
-        <v>322.1374944562475</v>
+        <v>322.1414741920701</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26406,28 +26598,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3532669667420211</v>
+        <v>0.3523420753548284</v>
       </c>
       <c r="J7" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K7" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1998539735867909</v>
+        <v>0.2020192150051872</v>
       </c>
       <c r="M7" t="n">
-        <v>4.238217628613424</v>
+        <v>4.205425651086705</v>
       </c>
       <c r="N7" t="n">
-        <v>27.37065169944301</v>
+        <v>27.11929103387409</v>
       </c>
       <c r="O7" t="n">
-        <v>5.231696827936707</v>
+        <v>5.207618556871662</v>
       </c>
       <c r="P7" t="n">
-        <v>317.3763829184302</v>
+        <v>317.3861685776271</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26484,28 +26676,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05720464963891496</v>
+        <v>0.05766385602966642</v>
       </c>
       <c r="J8" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K8" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006553584321853823</v>
+        <v>0.006808136441815771</v>
       </c>
       <c r="M8" t="n">
-        <v>4.174598211192444</v>
+        <v>4.147614964897287</v>
       </c>
       <c r="N8" t="n">
-        <v>27.14305989507826</v>
+        <v>26.79787384537221</v>
       </c>
       <c r="O8" t="n">
-        <v>5.209900180913091</v>
+        <v>5.176666286846412</v>
       </c>
       <c r="P8" t="n">
-        <v>311.4921220170107</v>
+        <v>311.4871026677399</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26543,7 +26735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I565"/>
+  <dimension ref="A1:I569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53075,17 +53267,205 @@
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>-36.95669431552662,175.84293626652817</t>
+          <t>-36.95673330054043,175.84288049059484</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>-36.95727189255739,175.84353335979915</t>
+          <t>-36.95732783261295,175.8434683873206</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-36.95323732985719,175.8416510162238</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-36.95396252586686,175.84164364047166</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-36.954675270592844,175.8417946388362</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-36.95538200732279,175.84206270726597</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-36.95607115878827,175.84240923736223</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>-36.956726970653634,175.84288954678215</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>-36.95732592182241,175.8434706066412</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-36.953236530621744,175.84166410960594</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-36.95396076509885,175.84165795140197</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-36.9546727836161,175.8418044884449</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-36.95537894724851,175.84207046276939</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-36.95606949636028,175.84241244223435</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-36.956722474658875,175.84289597921332</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>-36.957327569055636,175.84346869343378</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-36.95323364789735,175.8417113353061</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-36.953959659499475,175.84166693733457</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-36.9546737027163,175.8418008483722</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>-36.95538339826549,175.8420591820369</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>-36.956074679223725,175.84240245057376</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>-36.956722474658875,175.84289597921332</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>-36.957327569055636,175.84346869343378</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-36.953233606910615,175.84171200676147</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-36.95396069685199,175.84165850608917</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-36.9546737027163,175.8418008483722</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>-36.95538602118573,175.8420525344618</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>-36.95607433695918,175.84240311040045</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>-36.95672513676108,175.84289217053706</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>-36.95732684427302,175.84346953524508</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I569"/>
+  <dimension ref="A1:I572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19190,7 +19190,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>363.39</v>
+        <v>363.62</v>
       </c>
       <c r="C569" t="n">
         <v>354.09</v>
@@ -19211,6 +19211,105 @@
         <v>315.47</v>
       </c>
       <c r="I569" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>363.53</v>
+      </c>
+      <c r="C570" t="n">
+        <v>354.39</v>
+      </c>
+      <c r="D570" t="n">
+        <v>350</v>
+      </c>
+      <c r="E570" t="n">
+        <v>343.22</v>
+      </c>
+      <c r="F570" t="n">
+        <v>332.14</v>
+      </c>
+      <c r="G570" t="n">
+        <v>327.34</v>
+      </c>
+      <c r="H570" t="n">
+        <v>314.12</v>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="C571" t="n">
+        <v>355.64</v>
+      </c>
+      <c r="D571" t="n">
+        <v>350.46</v>
+      </c>
+      <c r="E571" t="n">
+        <v>343.76</v>
+      </c>
+      <c r="F571" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="G571" t="n">
+        <v>328.09</v>
+      </c>
+      <c r="H571" t="n">
+        <v>315.91</v>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="C572" t="n">
+        <v>356.03</v>
+      </c>
+      <c r="D572" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="E572" t="n">
+        <v>344.02</v>
+      </c>
+      <c r="F572" t="n">
+        <v>333.16</v>
+      </c>
+      <c r="G572" t="n">
+        <v>327.48</v>
+      </c>
+      <c r="H572" t="n">
+        <v>314.85</v>
+      </c>
+      <c r="I572" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19227,7 +19326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B681"/>
+  <dimension ref="A1:B685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26040,6 +26139,46 @@
       </c>
       <c r="B681" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -26208,28 +26347,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1716565187365519</v>
+        <v>-0.1604237610553859</v>
       </c>
       <c r="J2" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K2" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04344127986526081</v>
+        <v>0.0380260498808811</v>
       </c>
       <c r="M2" t="n">
-        <v>4.790825898506314</v>
+        <v>4.810041814787037</v>
       </c>
       <c r="N2" t="n">
-        <v>35.84410156328063</v>
+        <v>36.22209490607365</v>
       </c>
       <c r="O2" t="n">
-        <v>5.986994368068224</v>
+        <v>6.018479451329351</v>
       </c>
       <c r="P2" t="n">
-        <v>358.3595742180693</v>
+        <v>358.239340138864</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26286,28 +26425,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1971271580707542</v>
+        <v>0.200438761737829</v>
       </c>
       <c r="J3" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K3" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03931436332697236</v>
+        <v>0.04103613241616721</v>
       </c>
       <c r="M3" t="n">
-        <v>6.137640578777244</v>
+        <v>6.117574946062634</v>
       </c>
       <c r="N3" t="n">
-        <v>52.45791766357572</v>
+        <v>52.23400444746174</v>
       </c>
       <c r="O3" t="n">
-        <v>7.24278383382907</v>
+        <v>7.22730962720304</v>
       </c>
       <c r="P3" t="n">
-        <v>346.9553809311769</v>
+        <v>346.9199289987703</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26364,28 +26503,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.110737401312095</v>
+        <v>0.1137415777610726</v>
       </c>
       <c r="J4" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K4" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02158077775266976</v>
+        <v>0.02298516338402412</v>
       </c>
       <c r="M4" t="n">
-        <v>4.461462359452821</v>
+        <v>4.450698126721357</v>
       </c>
       <c r="N4" t="n">
-        <v>30.71387512579782</v>
+        <v>30.59469572172272</v>
       </c>
       <c r="O4" t="n">
-        <v>5.54201002577565</v>
+        <v>5.531247212132425</v>
       </c>
       <c r="P4" t="n">
-        <v>344.8304623161018</v>
+        <v>344.7983016599992</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26442,28 +26581,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3209526054453389</v>
+        <v>0.3219441977298328</v>
       </c>
       <c r="J5" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K5" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L5" t="n">
-        <v>0.163575994598583</v>
+        <v>0.1660987163113813</v>
       </c>
       <c r="M5" t="n">
-        <v>4.484560429853493</v>
+        <v>4.464546721975112</v>
       </c>
       <c r="N5" t="n">
-        <v>29.09891560002339</v>
+        <v>28.95100532714416</v>
       </c>
       <c r="O5" t="n">
-        <v>5.394341071903351</v>
+        <v>5.380613842968492</v>
       </c>
       <c r="P5" t="n">
-        <v>334.0887373979393</v>
+        <v>334.0781210275653</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26520,28 +26659,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.404126196948363</v>
+        <v>0.4038118408753053</v>
       </c>
       <c r="J6" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K6" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2316206193417861</v>
+        <v>0.2335346254121503</v>
       </c>
       <c r="M6" t="n">
-        <v>4.512935085244192</v>
+        <v>4.491534037983373</v>
       </c>
       <c r="N6" t="n">
-        <v>29.93095446145872</v>
+        <v>29.77511422624765</v>
       </c>
       <c r="O6" t="n">
-        <v>5.470918977782318</v>
+        <v>5.456657788999385</v>
       </c>
       <c r="P6" t="n">
-        <v>322.1414741920701</v>
+        <v>322.1448356854858</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26598,28 +26737,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3523420753548284</v>
+        <v>0.3531471348797702</v>
       </c>
       <c r="J7" t="n">
+        <v>571</v>
+      </c>
+      <c r="K7" t="n">
         <v>568</v>
       </c>
-      <c r="K7" t="n">
-        <v>565</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.2020192150051872</v>
+        <v>0.2047311485255859</v>
       </c>
       <c r="M7" t="n">
-        <v>4.205425651086705</v>
+        <v>4.187037006643158</v>
       </c>
       <c r="N7" t="n">
-        <v>27.11929103387409</v>
+        <v>26.97953171079407</v>
       </c>
       <c r="O7" t="n">
-        <v>5.207618556871662</v>
+        <v>5.194182487244174</v>
       </c>
       <c r="P7" t="n">
-        <v>317.3861685776271</v>
+        <v>317.3775390569305</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26676,28 +26815,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05766385602966642</v>
+        <v>0.05971947603413388</v>
       </c>
       <c r="J8" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K8" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006808136441815771</v>
+        <v>0.00738245126133108</v>
       </c>
       <c r="M8" t="n">
-        <v>4.147614964897287</v>
+        <v>4.1370461439917</v>
       </c>
       <c r="N8" t="n">
-        <v>26.79787384537221</v>
+        <v>26.67886908600881</v>
       </c>
       <c r="O8" t="n">
-        <v>5.176666286846412</v>
+        <v>5.165159153986332</v>
       </c>
       <c r="P8" t="n">
-        <v>311.4871026677399</v>
+        <v>311.4650977762774</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26735,7 +26874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I569"/>
+  <dimension ref="A1:I572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53430,7 +53569,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>-36.953233606910615,175.84171200676147</t>
+          <t>-36.95323344979475,175.8417145806739</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -53464,6 +53603,147 @@
         </is>
       </c>
       <c r="I569" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-36.95323351127488,175.84171357349078</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-36.953960287370805,175.84166183421237</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-36.9546737027163,175.8418008483722</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>-36.95538514687902,175.84205475032024</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>-36.95607541264773,175.84240103665942</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>-36.9567273847584,175.84288895432132</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>-36.95733573933199,175.84345920392374</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-36.95323296478458,175.84172252622955</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-36.95395858119818,175.84167570139198</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-36.95467245922777,175.8418057731764</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>-36.955383000853296,175.84206018924522</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>-36.95607154994778,175.84240848327465</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>-36.9567229479215,175.84289530211535</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>-36.95732394514251,175.84347290249002</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-36.953232848655304,175.84172442868655</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-36.953958048871996,175.84168002795187</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-36.954669945217766,175.84181572984528</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>-36.95538196758157,175.84206280798676</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>-36.95607042536415,175.84241065127642</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-36.95672655654885,175.84289013924294</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-36.957330929411306,175.8434647904904</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
